--- a/SGC-CKN/Excel/6df8959a-e523-4267-b08f-e261dd8ffead_Lô_CT-02_P2-41_D800_03-04-2026.xlsx
+++ b/SGC-CKN/Excel/6df8959a-e523-4267-b08f-e261dd8ffead_Lô_CT-02_P2-41_D800_03-04-2026.xlsx
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-1.88</v>
+        <v>-1.68</v>
       </c>
       <c r="H11" s="5">
         <v>0.25</v>
       </c>
       <c r="I11" s="5">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="J11" s="8">
-        <v>7.52</v>
+        <v>6.72</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1187,7 +1187,7 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-1.88</v>
+        <v>-1.68</v>
       </c>
       <c r="G12" s="9">
         <v>-4.78</v>
@@ -1196,10 +1196,10 @@
         <v>0.33</v>
       </c>
       <c r="I12" s="9">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J12" s="8">
-        <v>8.7</v>
+        <v>9.3</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1567,16 +1567,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-1.88</v>
+        <v>-1.68</v>
       </c>
       <c r="G2" s="5">
         <v>0.25</v>
       </c>
       <c r="H2" s="5">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="I2" s="8">
-        <v>7.52</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1593,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-1.88</v>
+        <v>-1.68</v>
       </c>
       <c r="F3" s="9">
         <v>-4.78</v>
@@ -1602,10 +1602,10 @@
         <v>0.33</v>
       </c>
       <c r="H3" s="9">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I3" s="8">
-        <v>8.7</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
